--- a/data/trans_camb/P1409-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1409-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,3</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,61</t>
+          <t>-1,98; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,68</t>
+          <t>-1,97; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,0</t>
+          <t>-3,58; 3,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,18</t>
+          <t>-3,29; 2,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,42</t>
+          <t>-1,62; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,71</t>
+          <t>-1,86; 2,44</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>-5,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 235,39</t>
+          <t>-55,55; 245,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,4; 390,81</t>
+          <t>-55,24; 289,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 135,09</t>
+          <t>-63,37; 142,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 146,74</t>
+          <t>-58,0; 119,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 113,32</t>
+          <t>-39,08; 132,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 178,37</t>
+          <t>-42,76; 110,23</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,46</t>
+          <t>-1,34; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,98</t>
+          <t>1,07; 6,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,56</t>
+          <t>-2,34; 2,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,13</t>
+          <t>-1,19; 3,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,42</t>
+          <t>-1,29; 1,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,16</t>
+          <t>0,64; 3,96</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>291,91%</t>
+          <t>273,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,52; 273,9</t>
+          <t>-75,7; 284,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,94; 1142,59</t>
+          <t>34,83; 1071,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,51; 119,01</t>
+          <t>-50,67; 113,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 138,65</t>
+          <t>-27,75; 135,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 90,79</t>
+          <t>-44,62; 95,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 242,26</t>
+          <t>17,42; 227,58</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,46</t>
+          <t>-1,92; 2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,05</t>
+          <t>0,29; 5,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,23</t>
+          <t>-1,02; 4,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,66</t>
+          <t>0,35; 5,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,6</t>
+          <t>-1,06; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,77</t>
+          <t>0,84; 4,41</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>132,05%</t>
+          <t>143,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142,28%</t>
+          <t>136,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>138,13%</t>
+          <t>140,09%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,05; 302,37</t>
+          <t>-71,31; 266,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 550,99</t>
+          <t>-10,0; 561,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 494,21</t>
+          <t>-46,5; 381,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 537,85</t>
+          <t>-0,42; 512,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 203,56</t>
+          <t>-39,62; 199,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,87; 378,6</t>
+          <t>24,72; 359,17</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,8</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,15</t>
+          <t>0,52</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,69</t>
+          <t>-0,39; 4,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 6,68</t>
+          <t>-0,68; 5,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,76</t>
+          <t>0,2; 5,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 44,86</t>
+          <t>-2,4; 1,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,61</t>
+          <t>0,75; 4,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 32,48</t>
+          <t>-0,99; 2,64</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103,64%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>605,26%</t>
+          <t>-15,43%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>437,36%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 454,86</t>
+          <t>-19,09; 471,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 579,25</t>
+          <t>-40,22; 534,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 435,51</t>
+          <t>1,11; 420,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 3555,19</t>
+          <t>-66,93; 112,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,62; 319,08</t>
+          <t>26,28; 313,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 2707,76</t>
+          <t>-36,96; 179,68</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,93</t>
+          <t>-2,71; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,74</t>
+          <t>-3,2; 2,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,36</t>
+          <t>-3,23; 3,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,45</t>
+          <t>-1,19; 5,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,42</t>
+          <t>-1,99; 2,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,56</t>
+          <t>-1,46; 2,76</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-18,71%</t>
+          <t>-27,44%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,57; 367,47</t>
+          <t>-77,18; 291,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 327,62</t>
+          <t>-100,0; 357,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 330,65</t>
+          <t>-75,7; 274,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 680,85</t>
+          <t>-33,17; 471,02</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 174,36</t>
+          <t>-55,03; 170,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 264,97</t>
+          <t>-44,06; 203,83</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,84</t>
+          <t>-3,87; 0,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,59</t>
+          <t>-1,61; 3,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,68</t>
+          <t>-2,93; 2,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,3</t>
+          <t>-0,61; 5,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,13</t>
+          <t>-2,6; 1,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,49</t>
+          <t>-0,47; 3,4</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 86,57</t>
+          <t>-91,16; 111,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 262,87</t>
+          <t>-43,83; 287,73</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,08; 167,66</t>
+          <t>-69,23; 173,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 292,78</t>
+          <t>-15,8; 271,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 73,66</t>
+          <t>-67,95; 62,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 179,5</t>
+          <t>-13,21; 178,75</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>4,16</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,53</t>
+          <t>-0,04; 3,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,31</t>
+          <t>0,48; 5,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,37</t>
+          <t>0,29; 4,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,29</t>
+          <t>3,5; 7,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,33</t>
+          <t>0,57; 3,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,9</t>
+          <t>2,64; 5,79</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>155,14%</t>
+          <t>171,11%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>166,76%</t>
+          <t>262,49%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>169,28%</t>
+          <t>227,72%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 398,65</t>
+          <t>-12,95; 400,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 567,35</t>
+          <t>3,52; 568,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,73; 318,64</t>
+          <t>5,26; 293,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11,59; 429,66</t>
+          <t>102,54; 592,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,92; 253,25</t>
+          <t>17,69; 254,17</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>48,61; 367,6</t>
+          <t>100,94; 472,81</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,85</t>
+          <t>-1,28; 1,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,84</t>
+          <t>0,27; 4,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,6</t>
+          <t>-0,51; 3,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,65</t>
+          <t>-0,47; 2,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,24</t>
+          <t>-0,27; 2,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,08</t>
+          <t>0,25; 2,73</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 144,5</t>
+          <t>-43,62; 136,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-48,31; 181,89</t>
+          <t>2,06; 285,77</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 183,48</t>
+          <t>-15,26; 178,95</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 139,35</t>
+          <t>-13,49; 148,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 120,55</t>
+          <t>-9,2; 116,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 111,65</t>
+          <t>2,03; 147,51</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,35</t>
+          <t>-0,11; 1,35</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,84</t>
+          <t>1,09; 2,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,15</t>
+          <t>0,46; 2,14</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,75</t>
+          <t>1,21; 2,89</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,54</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,59</t>
+          <t>1,38; 2,6</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>101,71%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>131,84%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>116,63%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 83,14</t>
+          <t>-4,99; 83,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31,05; 170,16</t>
+          <t>48,32; 179,61</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,84; 90,63</t>
+          <t>14,74; 94,22</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>47,02; 397,25</t>
+          <t>36,71; 127,86</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>15,43; 74,24</t>
+          <t>14,04; 73,66</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>64,6; 302,03</t>
+          <t>53,7; 126,17</t>
         </is>
       </c>
     </row>
